--- a/data/trans_camb/IP16B02-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16B02-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-38,31; 27,63</t>
+          <t>-38,33; 25,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-61,24; 16,56</t>
+          <t>-63,72; 13,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-34,79; 22,49</t>
+          <t>-33,34; 23,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,61</t>
+          <t>0,0; 44,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-26,91; 15,89</t>
+          <t>-26,22; 14,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,89; 14,41</t>
+          <t>-33,89; 12,78</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-41,9; 41,98</t>
+          <t>-42,35; 38,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-69,51; 22,51</t>
+          <t>-71,46; 19,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-36,23; 31,5</t>
+          <t>-33,57; 32,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 77,35</t>
+          <t>0,0; 78,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,87; 22,13</t>
+          <t>-29,67; 18,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,11; 18,01</t>
+          <t>-39,27; 17,35</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,92; 15,35</t>
+          <t>-15,49; 16,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 26,21</t>
+          <t>-3,53; 25,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 10,51</t>
+          <t>-11,86; 10,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 11,11</t>
+          <t>-15,31; 10,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 9,14</t>
+          <t>-10,35; 7,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 14,56</t>
+          <t>-5,23; 14,56</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,05; 22,98</t>
+          <t>-18,04; 24,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 40,12</t>
+          <t>-3,78; 40,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 12,82</t>
+          <t>-12,54; 12,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,39; 13,0</t>
+          <t>-16,14; 13,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 11,7</t>
+          <t>-11,43; 9,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 18,65</t>
+          <t>-5,67; 18,53</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 42,24</t>
+          <t>-9,28; 41,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-27,17; 26,7</t>
+          <t>-29,13; 27,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-28,25; 15,16</t>
+          <t>-28,61; 15,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,81; 20,04</t>
+          <t>-13,76; 19,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,21; 16,73</t>
+          <t>-12,56; 17,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,97; 16,39</t>
+          <t>-14,91; 14,95</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 77,29</t>
+          <t>-10,27; 74,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-29,71; 43,19</t>
+          <t>-30,91; 45,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-30,62; 18,25</t>
+          <t>-31,19; 18,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-16,29; 26,44</t>
+          <t>-14,41; 25,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-15,09; 21,78</t>
+          <t>-13,53; 23,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-16,21; 22,83</t>
+          <t>-16,23; 19,53</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 13,85</t>
+          <t>-10,37; 14,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 15,17</t>
+          <t>-9,19; 15,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 8,25</t>
+          <t>-10,42; 7,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 11,14</t>
+          <t>-6,46; 11,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 5,82</t>
+          <t>-8,75; 6,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 8,47</t>
+          <t>-6,52; 8,71</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 19,7</t>
+          <t>-11,89; 21,32</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 21,35</t>
+          <t>-10,72; 21,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 9,96</t>
+          <t>-11,34; 9,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 13,4</t>
+          <t>-6,99; 13,76</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 7,23</t>
+          <t>-9,76; 8,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 10,42</t>
+          <t>-7,42; 10,71</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16B02-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16B02-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-38,33; 25,73</t>
+          <t>-38,23; 28,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-63,72; 13,34</t>
+          <t>-64,43; 16,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-33,34; 23,15</t>
+          <t>-32,78; 28,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,01</t>
+          <t>0,0; 43,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-26,22; 14,18</t>
+          <t>-25,85; 15,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-33,89; 12,78</t>
+          <t>-32,28; 17,63</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-42,35; 38,58</t>
+          <t>-41,61; 42,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-71,46; 19,76</t>
+          <t>-71,09; 22,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-33,57; 32,54</t>
+          <t>-35,16; 41,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,6</t>
+          <t>0,0; 76,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,67; 18,28</t>
+          <t>-28,67; 21,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,27; 17,35</t>
+          <t>-35,8; 24,06</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,49; 16,49</t>
+          <t>-15,95; 16,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 25,94</t>
+          <t>-3,94; 27,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,86; 10,3</t>
+          <t>-10,1; 12,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 10,91</t>
+          <t>-12,66; 11,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 7,9</t>
+          <t>-10,56; 8,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 14,56</t>
+          <t>-5,16; 14,93</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,04; 24,77</t>
+          <t>-18,35; 22,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 40,04</t>
+          <t>-3,99; 43,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,54; 12,39</t>
+          <t>-10,77; 15,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,14; 13,01</t>
+          <t>-13,54; 13,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 9,82</t>
+          <t>-11,77; 10,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 18,53</t>
+          <t>-5,68; 19,8</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 41,23</t>
+          <t>-8,99; 41,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-29,13; 27,68</t>
+          <t>-26,89; 31,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-28,61; 15,57</t>
+          <t>-31,43; 15,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,76; 19,81</t>
+          <t>-13,84; 21,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,56; 17,87</t>
+          <t>-11,9; 16,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 14,95</t>
+          <t>-14,03; 15,54</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 74,8</t>
+          <t>-9,94; 75,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-30,91; 45,54</t>
+          <t>-29,36; 52,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-31,19; 18,95</t>
+          <t>-34,9; 18,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,41; 25,83</t>
+          <t>-13,97; 30,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 23,28</t>
+          <t>-12,9; 21,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-16,23; 19,53</t>
+          <t>-15,46; 20,2</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 14,61</t>
+          <t>-10,93; 14,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 15,33</t>
+          <t>-9,26; 15,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 7,91</t>
+          <t>-9,98; 8,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 11,36</t>
+          <t>-7,21; 10,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 6,65</t>
+          <t>-8,6; 5,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 8,71</t>
+          <t>-6,57; 9,21</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 21,32</t>
+          <t>-12,71; 19,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 21,07</t>
+          <t>-10,58; 22,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 9,56</t>
+          <t>-10,77; 10,62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 13,76</t>
+          <t>-7,67; 13,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 8,23</t>
+          <t>-9,66; 7,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 10,71</t>
+          <t>-7,37; 11,56</t>
         </is>
       </c>
     </row>
